--- a/api/src/excelreports/reportTemplates/DeviceAPIKeys.xlsx
+++ b/api/src/excelreports/reportTemplates/DeviceAPIKeys.xlsx
@@ -130,9 +130,6 @@
     <t>&lt;date&gt;</t>
   </si>
   <si>
-    <t>Country</t>
-  </si>
-  <si>
     <t>Created On</t>
   </si>
   <si>
@@ -173,6 +170,9 @@
   </si>
   <si>
     <t>Aspect DeviceApiKeys</t>
+  </si>
+  <si>
+    <t>County</t>
   </si>
 </sst>
 </file>
@@ -819,7 +819,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -837,48 +837,48 @@
     </row>
     <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="F5" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="G5" s="11" t="s">
         <v>48</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
